--- a/results/six_week_reports_20261028/report_06_結構驗證與最終比較.xlsx
+++ b/results/six_week_reports_20261028/report_06_結構驗證與最終比較.xlsx
@@ -12,8 +12,8 @@
     <sheet name="必要對照" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">必要對照!$A$1:$H$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">結果比較!$A$1:$H$74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">必要對照!$A$1:$H$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">結果比較!$A$1:$H$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">設定與說明!$A$1:$H$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">必要對照!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">結果比較!$1:$3</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="125">
   <si>
     <t>第6次｜結構驗證與最終比較</t>
   </si>
@@ -57,15 +57,15 @@
     <t>本次成功／總數</t>
   </si>
   <si>
-    <t>差：後−前 pp</t>
+    <t>vs前一次 pp</t>
+  </si>
+  <si>
+    <t>vs論文 pp</t>
   </si>
   <si>
     <t>案例組成</t>
   </si>
   <si>
-    <t>批次</t>
-  </si>
-  <si>
     <t>Tongji／Plot1</t>
   </si>
   <si>
@@ -75,10 +75,7 @@
     <t>待補</t>
   </si>
   <si>
-    <t>10對×10seed</t>
-  </si>
-  <si>
-    <t>seed31–40</t>
+    <t>10對×10seed；31–40</t>
   </si>
   <si>
     <t>Tongji／Plot2</t>
@@ -108,7 +105,7 @@
     <t>150/150</t>
   </si>
   <si>
-    <t>15對×10seed</t>
+    <t>15對×10seed；31–40</t>
   </si>
   <si>
     <t>Tongji四Plot屬同一dataset，ETH屬另一dataset；兩者不混算誤差平均。前後均同配對與seed，失敗與缺輸出都保留。原論文門檻與分母未確認一致，100%只能作報告值參考。</t>
@@ -367,6 +364,42 @@
   </si>
   <si>
     <t>全體成功數507/550、546/550、550/550，只累計成功數、不混算兩來源誤差。完整候選相對同backend的10cm方法額外救4次，均Plot4。Plot3較v2誤差增加約0.127mm；Plot4共同成功78例增加約0.733mm。</t>
+  </si>
+  <si>
+    <t>額外cold代表配對：同epoch與同backend，含提取＋cache</t>
+  </si>
+  <si>
+    <t>場景／配對</t>
+  </si>
+  <si>
+    <t>5cm參考＋v3 秒</t>
+  </si>
+  <si>
+    <t>完整multi_v3 秒</t>
+  </si>
+  <si>
+    <t>時間下降率</t>
+  </si>
+  <si>
+    <t>參考child RSS MiB</t>
+  </si>
+  <si>
+    <t>本次child RSS MiB</t>
+  </si>
+  <si>
+    <t>每法N</t>
+  </si>
+  <si>
+    <t>ETH-tree s1-s2</t>
+  </si>
+  <si>
+    <t>固定seed31單次；只作當次觀測</t>
+  </si>
+  <si>
+    <t>Tongji／Plot1 S2-S1</t>
+  </si>
+  <si>
+    <t>來源 results/professor_reports_20261026/evidence/C_cold_benchmark.json；SHA256 3bdbe233fab8514fef5a9eb9b855feaf41da377125e87090f51a439b43c9542d。epoch20261025T162801Z，Xeon8573C、quota4、OMP4、native串行；OS cache未清。RSS為最大native子程序，不含Python與page cache。每法每dataset僅1次，不能宣稱穩定速度排名。</t>
   </si>
 </sst>
 </file>
@@ -439,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -454,13 +487,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -942,13 +978,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -972,13 +1008,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1393,137 +1429,142 @@
       <c r="B8" s="5">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7">
+        <f>(100/100-B8)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5">
         <v>1</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7">
+        <f>(100/100-B9)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="7">
+        <f>(100/100-B10)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <f>(100/100-78/100)*100</f>
         <v>21.999999999999996</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="7">
+        <f>(100/100-B11)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="45" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="E12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="7">
         <f>(150/150-150/150)*100</f>
         <v>0.0</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>27</v>
+      <c r="G12" s="7">
+        <f>(150/150-B12)*100</f>
+        <v>0.0</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="44" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1535,7 +1576,7 @@
     </row>
     <row r="17" spans="1:8" ht="28" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1550,41 +1591,41 @@
         <v>5</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <v>5.2558</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>16.81264811104687</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>2.886600508789238</v>
       </c>
       <c r="F19" s="5">
@@ -1596,23 +1637,23 @@
         <v>0.45077809110140454</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8">
         <v>11.4808</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>54.50497163856171</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>1.185415858528841</v>
       </c>
       <c r="F20" s="5">
@@ -1624,23 +1665,23 @@
         <v>0.8967479741369208</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8">
         <v>4.8756</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>5.376450884068796</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <v>1.105659358968494</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <v>1.118315828811571</v>
       </c>
       <c r="F21" s="5">
@@ -1652,23 +1693,23 @@
         <v>0.7706301114095557</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8">
         <v>4.356</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>123.234678935483</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <v>864.7622010386872</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <v>3.392022720762585</v>
       </c>
       <c r="F22" s="5">
@@ -1680,23 +1721,23 @@
         <v>0.2212987326073037</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="7">
+        <v>23</v>
+      </c>
+      <c r="B23" s="8">
         <v>15.3427</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <v>12.62093021050369</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <v>0.6038135171016774</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <v>0.6038135170910868</v>
       </c>
       <c r="F23" s="5">
@@ -1708,12 +1749,12 @@
         <v>0.9606448984148105</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="44" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1725,7 +1766,7 @@
     </row>
     <row r="28" spans="1:8" ht="28" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1740,16 +1781,16 @@
         <v>5</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="45" customHeight="1">
@@ -1762,16 +1803,16 @@
       <c r="C30" s="5">
         <v>1</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <v>2.886600508789238</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="45" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="5">
         <v>1</v>
@@ -1779,16 +1820,16 @@
       <c r="C31" s="5">
         <v>1</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <v>1.185415858528841</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="5">
         <v>1</v>
@@ -1796,16 +1837,16 @@
       <c r="C32" s="5">
         <v>1</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="8">
         <v>1.105659358968494</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="8">
         <v>1.118315828811571</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="5">
         <v>0.78</v>
@@ -1813,16 +1854,16 @@
       <c r="C33" s="5">
         <v>1</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <v>864.7622010386872</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="8">
         <v>3.392022720762585</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="45" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="5">
         <v>1</v>
@@ -1830,10 +1871,10 @@
       <c r="C34" s="5">
         <v>1</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="8">
         <v>0.6038135171016774</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="8">
         <v>0.6038135170910868</v>
       </c>
     </row>
@@ -1912,7 +1953,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1924,91 +1965,91 @@
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="46" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2020,7 +2061,7 @@
     </row>
     <row r="16" spans="1:8" ht="28" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2035,88 +2076,88 @@
         <v>5</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <v>20.718</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>11.657</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7">
+        <v>17</v>
+      </c>
+      <c r="B19" s="8">
         <v>30.699</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>16.712</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8">
         <v>4.5596</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>8.3584</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="45" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="7">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8">
         <v>19.522</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>9.451599999999999</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="7">
+        <v>23</v>
+      </c>
+      <c r="B22" s="8">
         <v>3.0405</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <v>8.699199999999999</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2128,7 +2169,7 @@
     </row>
     <row r="26" spans="1:8" ht="38" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2140,7 +2181,7 @@
     </row>
     <row r="27" spans="1:8" ht="38" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2152,7 +2193,7 @@
     </row>
     <row r="28" spans="1:8" ht="38" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2164,7 +2205,7 @@
     </row>
     <row r="29" spans="1:8" ht="52" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2202,7 +2243,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -2251,7 +2292,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2263,28 +2304,28 @@
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
@@ -2300,10 +2341,10 @@
       <c r="D7" s="4">
         <v>100</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>2.886600508789238</v>
       </c>
       <c r="G7" s="5">
@@ -2311,12 +2352,12 @@
         <v>0.0</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4">
         <v>0</v>
@@ -2327,10 +2368,10 @@
       <c r="D8" s="4">
         <v>100</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>1.185415858528841</v>
       </c>
       <c r="G8" s="5">
@@ -2338,12 +2379,12 @@
         <v>0.0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -2354,10 +2395,10 @@
       <c r="D9" s="4">
         <v>100</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>1.105659358968494</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>1.118315828811571</v>
       </c>
       <c r="G9" s="5">
@@ -2365,12 +2406,12 @@
         <v>-0.011446988387891759</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="4">
         <v>22</v>
@@ -2381,10 +2422,10 @@
       <c r="D10" s="4">
         <v>78</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>2.185295580106831</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>2.258594574140534</v>
       </c>
       <c r="G10" s="5">
@@ -2392,12 +2433,12 @@
         <v>-0.03354191291144178</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="45" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="4">
         <v>0</v>
@@ -2408,10 +2449,10 @@
       <c r="D11" s="4">
         <v>150</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>0.6038135171016774</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>0.6038135170910868</v>
       </c>
       <c r="G11" s="5">
@@ -2419,12 +2460,12 @@
         <v>1.7539477433110922e-11</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2439,160 +2480,160 @@
         <v>5</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <v>0.0356799496337756</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <v>0.0356799496337756</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <v>2.919916286083178</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>2.919916286083178</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>801.3975566300001</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>2348.06727557</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="7">
+        <v>17</v>
+      </c>
+      <c r="B17" s="8">
         <v>0.055756468034214</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <v>0.055756468034214</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>1.035235466820431</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <v>1.035235466820431</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>942.32916675</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>4005.95130984</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="7">
+        <v>19</v>
+      </c>
+      <c r="B18" s="8">
         <v>0.01954336228675064</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <v>0.02032866491363596</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <v>1.096707992766773</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <v>1.107310874057868</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <v>570.34143955</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>2741.96727989</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="7">
+        <v>20</v>
+      </c>
+      <c r="B19" s="8">
         <v>28.79554128389449</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <v>0.02902219205984687</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>874.4183854103326</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <v>3.39372362588537</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>2294.81875456</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>6423.18030219</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="7">
+        <v>23</v>
+      </c>
+      <c r="B20" s="8">
         <v>0.05416013956593288</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>0.05416013956404717</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <v>0.4025727637267302</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <v>0.4025727637157485</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <v>1440.75008394</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <v>7082.222933306666</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2607,160 +2648,160 @@
         <v>5</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="H24" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <v>2.886600508815139</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="8">
         <v>2.886600508789238</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="8">
         <v>2.886600508789238</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="45" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <v>5.495887109547524</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="8">
         <v>1.185415858528841</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="8">
         <v>1.185415858528841</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="45" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <v>1.118306809353784</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="8">
         <v>1.118315828811571</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="8">
         <v>1.118315828811571</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="45" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <v>113.2921948004322</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="8">
         <v>103.2321322575001</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="8">
         <v>3.392022720762585</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="45" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="7">
+        <v>23</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="8">
         <v>0.5918335658071731</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="8">
         <v>0.6038135170910868</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="8">
         <v>0.6038135170910868</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="48" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2770,8 +2811,112 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
+    <row r="34" spans="1:8" ht="28" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8" ht="40" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="45" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="8">
+        <v>344.3097139259989</v>
+      </c>
+      <c r="C36" s="8">
+        <v>369.0621386269995</v>
+      </c>
+      <c r="D36" s="5">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(C36),B36&lt;&gt;0),(B36-C36)/B36,"待補")</f>
+        <v>-0.07188999816113378</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1422.484375</v>
+      </c>
+      <c r="F36" s="8">
+        <v>1422.359375</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="45" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="8">
+        <v>703.8726905160001</v>
+      </c>
+      <c r="C37" s="8">
+        <v>651.7896377920006</v>
+      </c>
+      <c r="D37" s="5">
+        <f>IF(AND(ISNUMBER(B37),ISNUMBER(C37),B37&lt;&gt;0),(B37-C37)/B37,"待補")</f>
+        <v>0.07399499003977288</v>
+      </c>
+      <c r="E37" s="8">
+        <v>2008.78125</v>
+      </c>
+      <c r="F37" s="8">
+        <v>2009.05859375</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="64" customHeight="1">
+      <c r="A40" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
@@ -2779,6 +2924,8 @@
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
